--- a/SCRIPT/SCRIPT/Canevas_Extraction_mSupply_DQA_v2.xlsx
+++ b/SCRIPT/SCRIPT/Canevas_Extraction_mSupply_DQA_v2.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Nouvelle PSP-CI / DAP · Spécification v2.0 (2026-08-28)</t>
+          <t>Nouvelle PSP-CI / DAP · Spécification v2.4 (2026-10-19)</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Les 45 derniers jours à chaque extraction (et non « depuis le dernier envoi »). Ce recouvrement permet de rattraper une semaine oubliée.</t>
+          <t>Du 1er jour du 2e mois avant la date d'extraction jusqu'à la date d'extraction (extraction du 12 octobre : du 1er août au 12 octobre), à chaque extraction et non « depuis le dernier envoi ». Le mois M-2 est ainsi extrait en entier, et le recouvrement rattrape une semaine oubliée.</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Transactions de la fenêtre (en-têtes), qualifiées par « nature ».</t>
+          <t>Transactions de la fenêtre (en-têtes), qualifiées par « nature » ; toutes les factures fournisseur si.</t>
         </is>
       </c>
     </row>
@@ -802,7 +802,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Réquisitions de la fenêtre.</t>
+          <t>Réquisitions de la fenêtre, et celles citées par une facture fournisseur si.</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2. « si » = facture fournisseur adressée au site, « rc » = réception enregistrée : confirmer.</t>
+          <t>2. Résolu (2026-10-14) : « si » = facture fournisseur adressée au site (nw, cn, fn), « rc » = reçu de paiement, transmis en nature encaissement.</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1045,7 +1044,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1265,7 +1263,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1541,7 +1538,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1553,6 +1550,7 @@
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="29" customWidth="1" min="9" max="9"/>
+    <col width="29" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1598,7 +1596,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Obligatoire. name_category3.description. Libellé exact : CSU, CSR, ESPC, HG, CHR, CHU, District sanitaire.</t>
+          <t>Obligatoire. Libellé exact : ESPC, HG, CHR, CHU, District sanitaire. Le préfixe du nom du site (CSU, CSR..., CHR, HG, CHU, DISTRICT SANITAIRE) l'emporte sur name_category3.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1614,6 +1612,11 @@
       <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Obligatoire. 5 (CSU/CSR/ESPC), 7 (HG/CHR), 10 (CHU/District).</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Facultatif. Type déduit de la seule catégorie mSupply (name_category3). Vide si la catégorie ne désigne pas un type (NPSP). Différent de type_structure : catégorie à corriger dans mSupply.</t>
         </is>
       </c>
     </row>
@@ -1663,6 +1666,11 @@
           <t>jour_limite_requisition</t>
         </is>
       </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>type_structure_msupply</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1710,7 +1718,13 @@
           <t>5</t>
         </is>
       </c>
-    </row>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ESPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1746,7 +1760,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1863,7 +1876,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1956,7 +1968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1973,6 +1985,9 @@
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
     <col width="17" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1985,7 +2000,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TRANSACTIONS · une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre.</t>
+          <t>TRANSACTIONS : une transaction (en-tête). Fenêtre = confirm_date ou finalised_date dans la fenêtre ; factures fournisseur si : toutes (nw, cn, fn) dont entry_date est dans la fenêtre.</t>
         </is>
       </c>
     </row>
@@ -2003,7 +2018,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, reception, ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
+          <t>Obligatoire. Valeur dérivée (voir §5.1 de la spécification). Valeurs : dispensation, distribution, facture_fournisseur, encaissement (rc, reçu de paiement), ajustement_positif, ajustement_negatif, retour_fournisseur, retour_client, autre.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -2043,7 +2058,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Obligatoire si nature = reception. transact.ship_date.</t>
+          <t>Facultatif. transact.ship_date.</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
@@ -2059,6 +2074,21 @@
       <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Obligatoire si nature = ajustement_positif ou ajustement_negatif. transact.comment.</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Obligatoire si statut = fn. transact.finalised_date (date de réception d'une facture si).</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Facture si seulement : la livraison qui l'a produite (transact.linked_transaction_id, dans un sens ou dans l'autre). Vide si aucune (site livré par la NPSP).</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>Facture si seulement : finalised_date de la livraison liée (mois où la facture doit être acceptée).</t>
         </is>
       </c>
     </row>
@@ -2133,6 +2163,21 @@
           <t>commentaire</t>
         </is>
       </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>date_finalisation</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>transaction_liee_id</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>date_finalisation_liee</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2147,7 +2192,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>reception</t>
+          <t>facture_fournisseur</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2157,7 +2202,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>rc</t>
+          <t>si</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -2196,12 +2241,24 @@
         </is>
       </c>
       <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="inlineStr">
-        <is>
-          <t>Reçu pour facture(s) 711</t>
-        </is>
-      </c>
-    </row>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>5b1e0c2a757411f1a120750a3f5057be</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2242,7 +2299,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2435,7 +2491,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2571,7 +2626,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="135" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
